--- a/public/BAO_CAO_HO_SO_HOC_SINH_SKYLINE.xlsx
+++ b/public/BAO_CAO_HO_SO_HOC_SINH_SKYLINE.xlsx
@@ -809,7 +809,7 @@
         <v>Kiểm tra lỗ hổng kiến thức để phân lớp học thuật và lộ trình phụ đạo ban đầu.</v>
       </c>
       <c r="E2" t="str">
-        <v>Mở Hồ sơ Học sinh 360° số hóa, cấp mã định danh studentCode duy nhất.</v>
+        <v>Mở Hồ sơ học tập HS số hóa, cấp mã định danh studentCode duy nhất.</v>
       </c>
     </row>
     <row r="3">
